--- a/artfynd/A 16370-2024 artfynd.xlsx
+++ b/artfynd/A 16370-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112606752</v>
+        <v>118177803</v>
       </c>
       <c r="B16" t="n">
-        <v>91032</v>
+        <v>78129</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,41 +2280,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Drosbacken, Dlr</t>
+          <t>Eländighetsgrubban (Eländighetsgrubban), Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>367938</v>
+        <v>368088</v>
       </c>
       <c r="R16" t="n">
-        <v>6860665</v>
+        <v>6860704</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2338,17 +2338,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,22 +2368,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Andreas Öster, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118177803</v>
+        <v>118177346</v>
       </c>
       <c r="B17" t="n">
-        <v>78129</v>
+        <v>79565</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,21 +2396,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2487,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118177346</v>
+        <v>118177817</v>
       </c>
       <c r="B18" t="n">
-        <v>79565</v>
+        <v>78221</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,21 +2508,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2599,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118177817</v>
+        <v>118177342</v>
       </c>
       <c r="B19" t="n">
-        <v>78221</v>
+        <v>79566</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,21 +2620,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2711,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118177342</v>
+        <v>118177801</v>
       </c>
       <c r="B20" t="n">
-        <v>79566</v>
+        <v>90749</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2723,25 +2728,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>65</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2823,10 +2828,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118177801</v>
+        <v>118177486</v>
       </c>
       <c r="B21" t="n">
-        <v>90749</v>
+        <v>79594</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2835,25 +2840,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2935,10 +2940,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118177486</v>
+        <v>118177837</v>
       </c>
       <c r="B22" t="n">
-        <v>79594</v>
+        <v>90654</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2947,25 +2952,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3044,118 +3049,6 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>118177837</v>
-      </c>
-      <c r="B23" t="n">
-        <v>90654</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>1503</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Gräddporing</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Sidera lenis</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Eländighetsgrubban (Eländighetsgrubban), Dlr</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>368088</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6860704</v>
-      </c>
-      <c r="S23" t="n">
-        <v>25</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Älvdalen</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Idre</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>08:25</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>08:25</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Andreas Öster, Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16370-2024 artfynd.xlsx
+++ b/artfynd/A 16370-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118177801</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118177803</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101154668</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109550901</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118177837</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101154661</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101154662</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1489,6 +1529,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101154664</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101154673</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1683,6 +1733,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101154674</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,6 +1846,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109550933</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1898,6 +1958,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118177342</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2000,6 +2065,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606752</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2102,6 +2172,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606753</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2204,6 +2279,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610400</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2306,6 +2386,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103410919</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2403,6 +2488,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101154656</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2500,6 +2590,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101154659</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2597,6 +2692,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101154667</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2694,6 +2794,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101154669</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2791,6 +2896,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101154671</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2893,6 +3003,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103410841</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103410842</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3103,6 +3223,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109550867</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3210,6 +3335,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118177346</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3307,6 +3437,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101154658</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3415,6 +3550,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109550919</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3522,6 +3662,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118177486</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3644,6 +3789,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109548684</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3752,6 +3902,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109550961</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3859,6 +4014,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118176553</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3966,8 +4126,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118177817</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>